--- a/EXEMPLE_Entrada_Mes_Demo.xlsx
+++ b/EXEMPLE_Entrada_Mes_Demo.xlsx
@@ -1137,8 +1137,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -1199,8 +1197,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
@@ -1766,12 +1762,38 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Novell-Nou1, Aina</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>nou-incorporat</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Nou professional (demo) — cobreix Dc 16-20</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="6" t="n"/>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Novell-Nou2, Bernat</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>nou-incorporat</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nou professional (demo) — cobreix Dc 16-20</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1853,7 +1875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF75"/>
+  <dimension ref="A1:AF77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4594,6 +4616,7 @@
       <c r="AE73" s="16" t="n"/>
       <c r="AF73" s="16" t="n"/>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
@@ -4618,6 +4641,20 @@
       <c r="J75" t="inlineStr">
         <is>
           <t>X = guàrdia assignada</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Novell-Nou1, Aina</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Novell-Nou2, Bernat</t>
         </is>
       </c>
     </row>
